--- a/web/public/forms/orig/o-pumjil-siheom.xlsx
+++ b/web/public/forms/orig/o-pumjil-siheom.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.현재진행 현장\어무골천 재해위험개선지구 정비사업\착공계\"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7E1E5D-75E3-406C-A476-698A0C46481F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>

--- a/web/public/forms/orig/o-pumjil-siheom.xlsx
+++ b/web/public/forms/orig/o-pumjil-siheom.xlsx
@@ -915,7 +915,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="71" t="inlineStr">
@@ -1826,7 +1826,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="71" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="71" t="inlineStr">
@@ -3912,7 +3912,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="71" t="inlineStr">
@@ -4259,7 +4259,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="71" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6720,7 +6720,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8936,7 +8936,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -10088,7 +10088,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="71" t="inlineStr">
@@ -10216,7 +10216,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="71" t="inlineStr">

--- a/web/public/forms/orig/o-pumjil-siheom.xlsx
+++ b/web/public/forms/orig/o-pumjil-siheom.xlsx
@@ -863,7 +863,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
